--- a/reports/group4_7_9_delivery_stats_2026-10-27.xlsx
+++ b/reports/group4_7_9_delivery_stats_2026-10-27.xlsx
@@ -15,7 +15,9 @@
     <sheet name="Not read" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Dedup" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Copy checks" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="43 types" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Mixed types" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Mixed signatures" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="43 types" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -788,62 +790,3772 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mixed types: readable -&gt; text</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7 types</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>5272</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4923</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>p1/group4_7_9/mixed_text</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>copy pending</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>paths whose every version is text: one .txt per path (as group 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mixed types: binary -&gt; whole</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5 types</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>p1/group4_7_9/mixed_binary/files</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>copy pending</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>160 distinct files, 2 ELF programs left out -&gt; 158; 153 dll / exe.deploy paths left out</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mixed types: readable -&gt; text</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3 types</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>inside 4.2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>3919448</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>p1/group4_7_9/group4_2/group4_7_9_mixed_text</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>copy pending</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dump 9, deploy 2, tmp 1; 4.2_R: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mixed types: binary -&gt; whole</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2 types</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>inside 4.2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>p1/group4_7_9/group4_2/group4_7_9_mixed_binary</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>copy pending</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dump / tmp; 12 dll / exe.deploy left out</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>SUM(E2:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="5">
-        <f>SUM(F2:F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="6">
-        <f>SUM(G2:G7)</f>
-        <v/>
-      </c>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Status 27 Oct 2026: the 26 types of these three routes are run and on the share (tracking in p1/group4_7_9_tracking). Of the 43 remaining types, 17 are still open: 7 sample first, 9 exclude + 1 list only waiting for confirmation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Containers' lines are counted before the dedup (1.09 B); the .txt removed by the dedup were identical copies of a kept path.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>GB = 10^9 bytes. Containers repo level: 896.96 GB before dedup, 339.67 GB of duplicate paths removed -&gt; 557.3 GB (= 520 GiB in du).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Earlier deliveries (not in this sheet): 4.7+4.9 group 1 text (160 types) and group 2 whole (117 types), repo level and inside 4.2, 23 Oct.</t>
-        </is>
-      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5">
+        <f>SUM(E2:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="5">
+        <f>SUM(F2:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="6">
+        <f>SUM(G2:G11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>Status 27 Oct 2026: the 26 types of these three routes are run and on the share (tracking in p1/group4_7_9_tracking). The 7 mixed types (deploy, dump, tmp, out, pbl-old, db_backup, simflows) are run per path by content - see 'Mixed types'; their copy is pending. Of the 43 remaining types, 10 are still open: 9 exclude + 1 list only waiting for confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Mixed types repo level: paths = all paths read (4,923 text + 328 binary + 21 no text); text lines / GB come with the copy check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Containers' lines are counted before the dedup (1.09 B); the .txt removed by the dedup were identical copies of a kept path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>GB = 10^9 bytes. Containers repo level: 896.96 GB before dedup, 339.67 GB of duplicate paths removed -&gt; 557.3 GB (= 520 GiB in du).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Earlier deliveries (not in this sheet): 4.7+4.9 group 1 text (160 types) and group 2 whole (117 types), repo level and inside 4.2, 23 Oct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
           <t>Credentials / keys (16 types) removed from scope (26 Oct).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>where</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>signature (first bytes)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>whole files to send</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>gzip (mongodump / gz archives)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>whole files to send</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>whole files to send</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>other binary</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>whole files to send</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ico</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>whole files to send</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>whole files to send</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>png</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>whole files to send</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>jpeg</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>whole files to send</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ms office (old)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>whole files to send</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>elf program -&gt; moved to _not_sent</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>whole files to send</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>postgres dump</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>moved to _not_sent</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>text-like (versions of paths sent as .txt)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>moved to _not_sent</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>utf-8 bom text (versions of paths sent as .txt)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>moved to _not_sent</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>program (MZ: dll / exe.deploy)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>repo level</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dll / exe.deploy versions left out</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>program (MZ)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>inside 4.2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>whole files to send</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>other binary</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>inside 4.2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>whole files to send</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>inside 4.2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>whole files to send</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ms office (old)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>inside 4.2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>moved to _not_sent</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>text-like</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>inside 4.2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>moved to _not_sent</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>utf-8 bom text</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>inside 4.2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>moved to _not_sent</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>program (MZ)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>108 of the 160 repo-level whole files are gzip: mongodump archives (global-rotation-composition *.gz.archive.dump, sdt-ey-isqc1-web Data/mongo.dump) - BSON inside the gzip; the biggest is 0.27 GB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Moved to _not_sent: versions of paths that go as .txt (their lines are already in the .txt) and the dll / exe programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sub_group</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>what it is</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>pii_risk</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>repos</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>files_vendored</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>files inside 4.2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>what is taken</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>script / steps</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>status (repo level)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>result (repo level)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status inside 4.2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>result (inside 4.2)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>next</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>parquet</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Parquet data files (test and output data, e.g. taxable income)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4548</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Group 2 (whole file) - tabular</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>the file itself, each distinct content once (history + today)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: tab_extract, tab_active, tab_inner</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2583 history + 553 today's distinct files</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>84 files, 58 distinct sent</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ORC data files (vendored test data)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Group 2 (whole file) - tabular</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>the file itself, each distinct content once (history + today)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: tab_extract, tab_active, tab_inner</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>18 history + 0 today's distinct files</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>20 files, 8 distinct sent</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>arrow</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apache Arrow files (Grafana test snapshots)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Group 2 (whole file) - tabular</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>the file itself, each distinct content once (history + today)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: tab_extract, tab_active, tab_inner</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>17 history + 0 today's distinct files</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>feather</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Feather data files (vendored)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Group 2 (whole file) - tabular</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>the file itself, each distinct content once (history + today)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: tab_extract, tab_active, tab_inner</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1 history + 0 today's distinct files</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4 files, 1 distinct sent</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>avro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avro data files (unit test data)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Group 2 (whole file) - tabular</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>the file itself, each distinct content once (history + today)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: tab_extract, tab_active, tab_inner</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>3 history + 1 today's distinct files</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>8 files, 8 distinct sent</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sav</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SPSS / IDL data files (mostly scipy test data)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>355</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>329</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Group 2 (whole file) - tabular</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>the file itself, each distinct content once (history + today)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: tab_extract, tab_active, tab_inner</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>59 history + 0 today's distinct files</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rds</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R data files; most are R package metadata from a committed R install</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>3807</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Group 3 (text) - data_to_text.py</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>one .txt per path, every value of every version + today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3,753 paths, 3,753 .txt, 607,680 lines</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>21 paths, 21 .txt, 11,384 lines</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>pickle</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pickled Python objects: NLTK models and app data (can hold any data)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Group 3 (text) - data_to_text.py</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>one .txt per path, every value of every version + today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>767 paths, 718 .txt, 40,345,346 lines</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>169 paths, 169 .txt, 6,497,737 lines</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>- (kept with the raw-scan lines, user 26 Oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ckpt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Model checkpoints (PyTorch Lightning)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Group 3 (text) - data_to_text.py</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>one .txt per path, every value of every version + today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>148 paths, 148 .txt, 92,762 lines</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>joblib</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>scikit-learn models (pickled; can hold training data)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Group 3 (text) - data_to_text.py</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>one .txt per path, every value of every version + today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>118 paths, 114 .txt, 4,438,634 lines</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>8 paths, 8 .txt, 10,332 lines</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>- (kept with the raw-scan lines, user 26 Oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>nippy</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Clojure Nippy serialized data (incl. "real_example")</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Group 3 (text) - data_to_text.py</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>one .txt per path, every value of every version + today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>64 paths, 64 .txt, 153,424 lines</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>rda</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R data files (R install, HiQPdf resource)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Group 3 (text) - data_to_text.py</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>one .txt per path, every value of every version + today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>65 paths, 62 .txt, 59,083 lines</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>npz</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NumPy archives (models, test data)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Group 3 (text) - data_to_text.py</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>one .txt per path, every value of every version + today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>40 paths, 40 .txt, 225 lines</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>5 paths, 5 .txt, 33 lines</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>rdata</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>R workspace data (any data)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Group 3 (text) - data_to_text.py</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>one .txt per path, every value of every version + today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>12 paths, 12 .txt, 302 lines</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>bson</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MongoDB BSON exports (test initial data)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Group 3 (text) - data_to_text.py</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>one .txt per path, every value of every version + today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>8 paths, 8 .txt, 9,281 lines</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>pk</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pickle data (sanction_update_status.pk)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Group 3 (text) - data_to_text.py</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>one .txt per path, every value of every version + today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>5 paths, 5 .txt, 48 lines</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>npy</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NumPy arrays (mostly library test data)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Group 3 (text) - data_to_text.py</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>one .txt per path, every value of every version + today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>22 paths, 5 .txt, 5,642 lines</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>13 paths, 8 .txt, 8,897 lines</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>pbix</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Power BI reports; usually embed the imported data (e.g. HR &amp; payroll, vendors)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>15540</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Containers - data + images only (bi_to_data.py)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>data model tables (pbixray) as text; images whole</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>15,104 paths, 15,034 .txt (before dedup), 1,093,145,012 lines, 2,676 images</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>145 paths, 139 .txt, 11,309,328 lines, 23 images</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>-  (262 live-connection versions without data; 5 damaged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>pbit</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Power BI templates (model and queries, no data)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Containers - data + images only (bi_to_data.py)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>images only (templates hold no data)</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>616 paths, 0 .txt (before dedup), 0 lines, 70 images</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>13 paths, 0 .txt, 0 lines, 1 images</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>dbc</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Databricks notebook archives (zip of JSON notebooks)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>784</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Containers - data + images only (bi_to_data.py)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>notebook outputs (result tables, text, html) as text; images in outputs whole; no code</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>763 paths, 78 .txt (before dedup), 23,835 lines, 0 images</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2 paths, 2 .txt, 6,676 lines, 0 images</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>460 plain-text notebook versions not read - send as text? (open)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mwb</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MySQL Workbench models (zip; may hold sample rows)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Containers - data + images only (bi_to_data.py)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>sample rows of its SQLite file as text; images whole</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>52 paths, 52 .txt (before dedup), 890 lines, 0 images</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>pbi</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Power BI files</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Containers - data + images only (bi_to_data.py)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>data model tables (pbixray) as text; images whole</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2 paths, 2 .txt (before dedup), 130,712 lines, 1 images</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>twbx</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tableau packaged workbooks (embed data)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Containers - data + images only (bi_to_data.py)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>.hyper extract tables (Hyper API) as text; packaged data files and images whole</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1 paths, 1 .txt (before dedup), 58,749 lines, 0 images</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>1 paths, 0 .txt, 0 lines, 1 images</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>numbers</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apple Numbers spreadsheet (submission_3)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Containers - data + images only (bi_to_data.py)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>cell text of the tables as text (numbers not); preview image whole</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>1 paths, 1 .txt (before dedup), 138 lines, 3 images</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>1 paths, 1 .txt, 138 lines, 3 images</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>kmz</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Google Earth data (wind farm locations)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Containers - data + images only (bi_to_data.py)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>placemarks (name, description, address, fields, point) as text; images whole</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2 paths, 2 .txt (before dedup), 252 lines, 0 images</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>qgz</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>QGIS project</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Containers - data + images only (bi_to_data.py)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>images only (no data)</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Copied 27 Oct</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1 paths, 0 .txt (before dedup), 0 lines, 0 images</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>deploy</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ClickOnce published files: *.dll.deploy, *.exe.deploy (binaries) and *.config.deploy (app config)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>5129</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Mixed: per path by content</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>text paths as .txt (group 1), binary paths whole (group 2); dll / exe programs left out</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_mixed.sh; check_group4_7_9_mixed.py</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Run 27 Oct, copy pending</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>4,850 text, 90 whole, 153 left out</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Run 27 Oct, copy pending</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2 text, 12 left out</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>tmp</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Mixed temp files: Office temp files, csproj backups, wasm</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Mixed: per path by content</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>text paths as .txt (group 1), binary paths whole (group 2); dll / exe programs left out</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_mixed.sh; check_group4_7_9_mixed.py</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Run 27 Oct, copy pending</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>47 text, 31 whole, 15 no text</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Run 27 Oct, copy pending</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1 text, 3 whole, 2 no text</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Group 4.7</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Mixed: a.out binaries, nohup.out logs, test outputs</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Mixed: per path by content</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>text paths as .txt (group 1), binary paths whole (group 2); dll / exe programs left out</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_mixed.sh; check_group4_7_9_mixed.py</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Run 27 Oct, copy pending</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>24 text, 11 whole, 3 no text</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>none read</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>10 paths, all vendored / old versions</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>dump</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Database / LDAP dumps (accesscontrol.dump, enumeration.dump)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Mixed: per path by content</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>text paths as .txt (group 1), binary paths whole (group 2); dll / exe programs left out</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_mixed.sh; check_group4_7_9_mixed.py</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Run 27 Oct, copy pending</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>41 whole, 1 no text</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Run 27 Oct, copy pending</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>9 text, 8 whole</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>db_backup</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Backup or temporary copy of another file</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Mixed: per path by content</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>text paths as .txt (group 1), binary paths whole (group 2); dll / exe programs left out</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_mixed.sh; check_group4_7_9_mixed.py</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Run 27 Oct, copy pending</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2 no text</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>- (nothing to send: no text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>pbl-old</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Backup or temporary copy of another file</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Mixed: per path by content</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>text paths as .txt (group 1), binary paths whole (group 2); dll / exe programs left out</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_mixed.sh; check_group4_7_9_mixed.py</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Run 27 Oct, copy pending</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2 whole</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>simflows</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Simulation flow files (client documents)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Mixed: per path by content</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>text paths as .txt (group 1), binary paths whole (group 2); dll / exe programs left out</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>run_group4_7_9_mixed.sh; check_group4_7_9_mixed.py</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Run 27 Oct, copy pending</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2 text</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>arff</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Weka datasets in vendored tests</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Exclude (proposed)</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Waiting for confirmation</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Confirm exclude: Weka datasets in vendored tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>xcuserstate</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Xcode user UI state (binary)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Exclude (proposed)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Waiting for confirmation</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Waiting for confirmation</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Confirm exclude: Xcode user UI state (binary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>test-db</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Test database fixtures (SQLite test files)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Exclude (proposed)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Waiting for confirmation</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Confirm exclude: Test database fixtures (SQLite test files)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>train</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Training data files</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Exclude (proposed)</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Waiting for confirmation</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Confirm exclude: Training data files</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sublime-workspace</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sublime Text workspace state</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Exclude (proposed)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Waiting for confirmation</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Waiting for confirmation</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Confirm exclude: Sublime Text workspace state</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ftz</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>fastText language model</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Exclude (proposed)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Waiting for confirmation</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Confirm exclude: fastText language model</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>rsuser</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SSRS user settings</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Exclude (proposed)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Waiting for confirmation</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Waiting for confirmation</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Confirm exclude: SSRS user settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2ph</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Upload temp files (RadUploadTemp)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Exclude (proposed)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Waiting for confirmation</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Confirm exclude: Upload temp files (RadUploadTemp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>mmdb</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Group 4.9</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GeoIP database</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Exclude (proposed)</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Waiting for confirmation</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Waiting for confirmation</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Confirm exclude: GeoIP database</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>jar1</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Group 4.7</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Misspelled .jar</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>List only (proposed)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>path list with commits (misspelled .jar)</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ext_path_list.py</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Waiting for confirmation</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>not inside the archives</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Confirm list only</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Done and copied 27 Oct: 26 types (6 tabular, 11 group 3 text, 9 containers). Run 27 Oct, copy pending: 7 mixed types. Open: 9 exclude + jar1 list only waiting for confirmation.</t>
         </is>
       </c>
     </row>
@@ -858,7 +4570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1772,59 +5484,330 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>deploy</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mixed: text</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>.txt</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>4850</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <f>D28+E28+F28+G28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>dump</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mixed: text</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>.txt</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
+        <f>D29+E29+F29+G29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>tmp</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mixed: text</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>.txt</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <f>D30+E30+F30+G30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mixed: text</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>.txt</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2">
+        <f>D31+E31+F31+G31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>pbl-old</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mixed: text</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>.txt</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <f>D32+E32+F32+G32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>db_backup</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mixed: text</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>.txt</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2">
+        <f>D33+E33+F33+G33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>simflows</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Mixed: text</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>.txt</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2">
+        <f>D34+E34+F34+G34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>deploy, dump, tmp, out, pbl-old</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Mixed: whole</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>whole file</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2">
+        <f>D35+E35+F35+G35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="5">
-        <f>SUM(D2:D27)</f>
-        <v/>
-      </c>
-      <c r="E28" s="5">
-        <f>SUM(E2:E27)</f>
-        <v/>
-      </c>
-      <c r="F28" s="5">
-        <f>SUM(F2:F27)</f>
-        <v/>
-      </c>
-      <c r="G28" s="5">
-        <f>SUM(G2:G27)</f>
-        <v/>
-      </c>
-      <c r="H28" s="5">
-        <f>SUM(H2:H27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Files on the share per type (27 Oct). 4.2_R: none of these 26 types.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="5">
+        <f>SUM(D2:D35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="5">
+        <f>SUM(E2:E35)</f>
+        <v/>
+      </c>
+      <c r="F36" s="5">
+        <f>SUM(F2:F35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="5">
+        <f>SUM(G2:G35)</f>
+        <v/>
+      </c>
+      <c r="H36" s="5">
+        <f>SUM(H2:H35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Files on the share per type (27 Oct). 4.2_R: none of these 33 types.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Group 3 text: one .txt per path; 4,929 repo level counted (1 of them goes as __case2 after the case fix).</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Tabular: distinct whole files, history + today's (named by blob id).</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Containers: .txt after the dedup (repo scope) + images; the .pbix etc. themselves are not sent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Mixed: .txt = paths whose every version is text; whole files (one row, all types) = distinct binary contents, dll / exe and ELF programs left out. Copy pending.</t>
         </is>
       </c>
     </row>
@@ -5026,2252 +9009,1072 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>where</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>sub_group</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>what it is</t>
+          <t>inner extension (a.xsd.deploy -&gt; xsd)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>pii_risk</t>
+          <t>text -&gt; .txt</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>repos</t>
+          <t>binary -&gt; whole file</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>files</t>
+          <t>left out: dll / exe program</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>files_vendored</t>
+          <t>no text</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>files inside 4.2</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>plan</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>what is taken</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>script / steps</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>status (repo level)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>result (repo level)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>status inside 4.2</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>result (inside 4.2)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>next</t>
+          <t>paths</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>parquet</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Parquet data files (test and output data, e.g. taxable income)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+          <t>xsd</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3392</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4548</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Group 2 (whole file) - tabular</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>the file itself, each distinct content once (history + today)</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: tab_extract, tab_active, tab_inner</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2583 history + 553 today's distinct files</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>84 files, 58 distinct sent</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <f>D2+E2+F2+G2</f>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>orc</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ORC data files (vendored test data)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>xsl</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1006</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Group 2 (whole file) - tabular</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>the file itself, each distinct content once (history + today)</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: tab_extract, tab_active, tab_inner</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>18 history + 0 today's distinct files</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>20 files, 8 distinct sent</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <f>D3+E3+F3+G3</f>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>arrow</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Apache Arrow files (Grafana test snapshots)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+          <t>xml</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>364</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Group 2 (whole file) - tabular</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>the file itself, each distinct content once (history + today)</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: tab_extract, tab_active, tab_inner</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>17 history + 0 today's distinct files</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <f>D4+E4+F4+G4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>feather</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Feather data files (vendored)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Group 2 (whole file) - tabular</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>the file itself, each distinct content once (history + today)</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: tab_extract, tab_active, tab_inner</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1 history + 0 today's distinct files</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>4 files, 1 distinct sent</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <f>D5+E5+F5+G5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>avro</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avro data files (unit test data)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Group 2 (whole file) - tabular</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>the file itself, each distinct content once (history + today)</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: tab_extract, tab_active, tab_inner</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>3 history + 1 today's distinct files</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>8 files, 8 distinct sent</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H6" s="2">
+        <f>D6+E6+F6+G6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sav</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SPSS / IDL data files (mostly scipy test data)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>xslt</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>355</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>329</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Group 2 (whole file) - tabular</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>the file itself, each distinct content once (history + today)</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: tab_extract, tab_active, tab_inner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>59 history + 0 today's distinct files</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <f>D7+E7+F7+G7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rds</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>R data files; most are R package metadata from a committed R install</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>htm</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>3807</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Group 3 (text) - data_to_text.py</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>one .txt per path, every value of every version + today</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>3,753 paths, 3,753 .txt, 607,680 lines</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>21 paths, 21 .txt, 11,384 lines</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <f>D8+E8+F8+G8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pickle</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pickled Python objects: NLTK models and app data (can hold any data)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>783</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>169</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Group 3 (text) - data_to_text.py</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>one .txt per path, every value of every version + today</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>767 paths, 718 .txt, 40,345,346 lines</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>169 paths, 169 .txt, 6,497,737 lines</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>- (kept with the raw-scan lines, user 26 Oct)</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <f>D9+E9+F9+G9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ckpt</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Model checkpoints (PyTorch Lightning)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+          <t>png</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Group 3 (text) - data_to_text.py</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>one .txt per path, every value of every version + today</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>148 paths, 148 .txt, 92,762 lines</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H10" s="2">
+        <f>D10+E10+F10+G10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>joblib</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>scikit-learn models (pickled; can hold training data)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>jpg</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Group 3 (text) - data_to_text.py</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>one .txt per path, every value of every version + today</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>118 paths, 114 .txt, 4,438,634 lines</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>8 paths, 8 .txt, 10,332 lines</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>- (kept with the raw-scan lines, user 26 Oct)</t>
-        </is>
+      <c r="H11" s="2">
+        <f>D11+E11+F11+G11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nippy</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Clojure Nippy serialized data (incl. "real_example")</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Group 3 (text) - data_to_text.py</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>one .txt per path, every value of every version + today</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>64 paths, 64 .txt, 153,424 lines</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H12" s="2">
+        <f>D12+E12+F12+G12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rda</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>R data files (R install, HiQPdf resource)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>ico</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Group 3 (text) - data_to_text.py</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>one .txt per path, every value of every version + today</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>65 paths, 62 .txt, 59,083 lines</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H13" s="2">
+        <f>D13+E13+F13+G13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>npz</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NumPy archives (models, test data)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>kat</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>195</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Group 3 (text) - data_to_text.py</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>one .txt per path, every value of every version + today</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>40 paths, 40 .txt, 225 lines</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>5 paths, 5 .txt, 33 lines</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <f>D14+E14+F14+G14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rdata</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>R workspace data (any data)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+          <t>dll</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Group 3 (text) - data_to_text.py</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>one .txt per path, every value of every version + today</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>12 paths, 12 .txt, 302 lines</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H15" s="2">
+        <f>D15+E15+F15+G15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bson</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MongoDB BSON exports (test initial data)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+          <t>exe</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Group 3 (text) - data_to_text.py</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>one .txt per path, every value of every version + today</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>8 paths, 8 .txt, 9,281 lines</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H16" s="2">
+        <f>D16+E16+F16+G16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pk</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>dump</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pickle data (sanction_update_status.pk)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Group 3 (text) - data_to_text.py</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>one .txt per path, every value of every version + today</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>5 paths, 5 .txt, 48 lines</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H17" s="2">
+        <f>D17+E17+F17+G17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>npy</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>dump</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NumPy arrays (mostly library test data)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>archive (.gz.archive.dump)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>394</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Group 3 (text) - data_to_text.py</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>one .txt per path, every value of every version + today</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_group3.sh: extract, text, inner</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>22 paths, 5 .txt, 5,642 lines</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>13 paths, 8 .txt, 8,897 lines</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <f>D18+E18+F18+G18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pbix</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>tmp</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Power BI reports; usually embed the imported data (e.g. HR &amp; payroll, vendors)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>117</v>
+        <v>27</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>15540</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Containers - data + images only (bi_to_data.py)</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>data model tables (pbixray) as text; images whole</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>15,104 paths, 15,034 .txt (before dedup), 1,093,145,012 lines, 2,676 images</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>145 paths, 139 .txt, 11,309,328 lines, 23 images</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>-  (262 live-connection versions without data; 5 damaged)</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H19" s="2">
+        <f>D19+E19+F19+G19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pbit</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>tmp</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Power BI templates (model and queries, no data)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>backup / backup (1)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>648</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Containers - data + images only (bi_to_data.py)</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>images only (templates hold no data)</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>616 paths, 0 .txt (before dedup), 0 lines, 70 images</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>13 paths, 0 .txt, 0 lines, 1 images</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <f>D20+E20+F20+G20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dbc</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>tmp</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Databricks notebook archives (zip of JSON notebooks)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+          <t>json / tsx</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>784</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Containers - data + images only (bi_to_data.py)</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>notebook outputs (result tables, text, html) as text; images in outputs whole; no code</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>763 paths, 78 .txt (before dedup), 23,835 lines, 0 images</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2 paths, 2 .txt, 6,676 lines, 0 images</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>460 plain-text notebook versions not read - send as text? (open)</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H21" s="2">
+        <f>D21+E21+F21+G21</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mwb</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>tmp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MySQL Workbench models (zip; may hold sample rows)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>wasm</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Containers - data + images only (bi_to_data.py)</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>sample rows of its SQLite file as text; images whole</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>52 paths, 52 .txt (before dedup), 890 lines, 0 images</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H22" s="2">
+        <f>D22+E22+F22+G22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pbi</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>tmp</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Power BI files</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>zip... (Office temp names)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Containers - data + images only (bi_to_data.py)</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>data model tables (pbixray) as text; images whole</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2 paths, 2 .txt (before dedup), 130,712 lines, 1 images</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H23" s="2">
+        <f>D23+E23+F23+G23</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>twbx</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>tmp</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tableau packaged workbooks (embed data)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Containers - data + images only (bi_to_data.py)</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>.hyper extract tables (Hyper API) as text; packaged data files and images whole</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1 paths, 1 .txt (before dedup), 58,749 lines, 0 images</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>1 paths, 0 .txt, 0 lines, 1 images</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H24" s="2">
+        <f>D24+E24+F24+G24</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>numbers</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>out</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Apple Numbers spreadsheet (submission_3)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>18</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Containers - data + images only (bi_to_data.py)</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>cell text of the tables as text (numbers not); preview image whole</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>1 paths, 1 .txt (before dedup), 138 lines, 3 images</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>1 paths, 1 .txt, 138 lines, 3 images</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="H25" s="2">
+        <f>D25+E25+F25+G25</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kmz</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>out</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Google Earth data (wind farm locations)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>xml</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Containers - data + images only (bi_to_data.py)</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>placemarks (name, description, address, fields, point) as text; images whole</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2 paths, 2 .txt (before dedup), 252 lines, 0 images</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H26" s="2">
+        <f>D26+E26+F26+G26</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>qgz</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>pbl-old</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>QGIS project</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Containers - data + images only (bi_to_data.py)</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>images only (no data)</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>run_group4_7_9_bi.sh: extract, data, inner</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Copied 27 Oct</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>1 paths, 0 .txt (before dedup), 0 lines, 0 images</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H27" s="2">
+        <f>D27+E27+F27+G27</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>deploy</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>simflows</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ClickOnce published files: *.dll.deploy, *.exe.deploy (binaries) and *.config.deploy (app config)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>5129</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Sample first</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>ClickOnce: *.config.deploy (app config) as group 1 text, *.dll / *.exe.deploy binaries out - count the split first</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>sample_ext_files.py - not run</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Sample, then route</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <f>D28+E28+F28+G28</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tmp</t>
+          <t>repo level</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>db_backup</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mixed temp files: Office temp files, csproj backups, wasm</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Sample first</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>mixed: Office temp files, csproj backups, wasm</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>sample_ext_files.py - not run</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Sample, then route</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="H29" s="2">
+        <f>D29+E29+F29+G29</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>inside 4.2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Group 4.7</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mixed: a.out binaries, nohup.out logs, test outputs</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Sample first</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>mixed: a.out binaries, nohup.out logs, test outputs</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>sample_ext_files.py - not run</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Sample, then route</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <f>D30+E30+F30+G30</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dump</t>
+          <t>inside 4.2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Database / LDAP dumps (accesscontrol.dump, enumeration.dump)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+          <t>dll</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Sample first</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>database / LDAP dumps - likely real data</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>sample_ext_files.py - not run</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Sample, then route</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H31" s="2">
+        <f>D31+E31+F31+G31</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>db_backup</t>
+          <t>inside 4.2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Backup or temporary copy of another file</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>exe</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>2</v>
@@ -7279,767 +10082,178 @@
       <c r="G32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Sample first</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>backup copy of another file</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>sample_ext_files.py - not run</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Sample, then route</t>
-        </is>
+      <c r="H32" s="2">
+        <f>D32+E32+F32+G32</f>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pbl-old</t>
+          <t>inside 4.2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>dump</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Backup or temporary copy of another file</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Sample first</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>backup copy of another file</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>sample_ext_files.py - not run</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Sample, then route</t>
-        </is>
+      <c r="H33" s="2">
+        <f>D33+E33+F33+G33</f>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>simflows</t>
+          <t>inside 4.2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>tmp</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Simulation flow files (client documents)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>backup</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Sample first</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>simulation flow files (client documents)</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>sample_ext_files.py - not run</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Sample, then route</t>
-        </is>
+      <c r="H34" s="2">
+        <f>D34+E34+F34+G34</f>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>arff</t>
+          <t>inside 4.2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Group 4.9</t>
+          <t>tmp</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Weka datasets in vendored tests</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Exclude (proposed)</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>nothing</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Waiting for confirmation</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Confirm exclude: Weka datasets in vendored tests</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="H35" s="2">
+        <f>D35+E35+F35+G35</f>
+        <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>xcuserstate</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Group 4.9</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Xcode user UI state (binary)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Exclude (proposed)</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>nothing</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Waiting for confirmation</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Waiting for confirmation</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Confirm exclude: Xcode user UI state (binary)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>test-db</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Group 4.9</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Test database fixtures (SQLite test files)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Exclude (proposed)</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>nothing</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Waiting for confirmation</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Confirm exclude: Test database fixtures (SQLite test files)</t>
-        </is>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="5">
+        <f>SUM(D2:D35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="5">
+        <f>SUM(E2:E35)</f>
+        <v/>
+      </c>
+      <c r="F36" s="5">
+        <f>SUM(F2:F35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="5">
+        <f>SUM(G2:G35)</f>
+        <v/>
+      </c>
+      <c r="H36" s="5">
+        <f>SUM(H2:H35)</f>
+        <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Group 4.9</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Training data files</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Exclude (proposed)</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>nothing</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Waiting for confirmation</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Confirm exclude: Training data files</t>
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Why: for these 7 types the name does not say what is inside - one type holds text and binary files (.deploy is a ClickOnce suffix on any file: XML / schemas / config, images, and .dll / .exe programs; .dump / .out / .tmp can be text logs, SQL / LDAP / Mongo dumps or raw binary). So each path is routed by its content, not by its type.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>sublime-workspace</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Group 4.9</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Sublime Text workspace state</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Exclude (proposed)</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>nothing</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Waiting for confirmation</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Waiting for confirmation</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Confirm exclude: Sublime Text workspace state</t>
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Text: every version of the path (history + today's) is readable -&gt; one .txt with every line once (as group 1): the scanner reads it directly, repeated lines across versions go once, the .txt mirrors the repo path.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ftz</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Group 4.9</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>fastText language model</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Exclude (proposed)</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>nothing</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Waiting for confirmation</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Confirm exclude: fastText language model</t>
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Whole file: any version is binary -&gt; the file itself, each distinct content once, named by blob id (as group 2): binary can't be cut into lines; sent whole the scanner opens it with its own readers.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>rsuser</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Group 4.9</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>SSRS user settings</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Exclude (proposed)</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>nothing</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Waiting for confirmation</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Waiting for confirmation</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Confirm exclude: SSRS user settings</t>
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Left out: .dll / .exe.deploy (compiled programs, not data; user 27 Oct) and 2 ELF programs found by content among the binaries; paths with no text in any version (nothing to scan).</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2ph</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Group 4.9</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Upload temp files (RadUploadTemp)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Exclude (proposed)</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>nothing</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Waiting for confirmation</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Confirm exclude: Upload temp files (RadUploadTemp)</t>
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Check (check_group4_7_9_mixed.py): names and contents agree - every xsd / xsl / xml / config went as text, every png / jpg / pdf / ico whole, all 85 dll / exe versions left out are MZ programs. Repo level total = 5,272 paths (4,923 text, 175 whole, 153 left out, 21 no text).</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>mmdb</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Group 4.9</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>GeoIP database</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Exclude (proposed)</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>nothing</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Waiting for confirmation</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Waiting for confirmation</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Confirm exclude: GeoIP database</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>jar1</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Group 4.7</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Misspelled .jar</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>List only (proposed)</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>path list with commits (misspelled .jar)</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>ext_path_list.py</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Waiting for confirmation</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>not inside the archives</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Confirm list only</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>Done and copied 27 Oct: 26 types (6 tabular, 11 group 3 text, 9 containers). Open: 7 sample first; 9 exclude + jar1 list only waiting for confirmation.</t>
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Inside 4.2: 'out' has 10 paths, all vendored or old versions, so none read. 4.2_R: none of these types.</t>
         </is>
       </c>
     </row>
